--- a/artfynd/A 6963-2023 artfynd.xlsx
+++ b/artfynd/A 6963-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115944206</v>
+        <v>115944239</v>
       </c>
       <c r="B2" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530510</v>
+        <v>530379</v>
       </c>
       <c r="R2" t="n">
-        <v>7237349</v>
+        <v>7237307</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>5728</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -775,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115944267</v>
+        <v>115944214</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530334</v>
+        <v>530487</v>
       </c>
       <c r="R3" t="n">
-        <v>7237280</v>
+        <v>7237338</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,7 +865,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>5714</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -886,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115944214</v>
+        <v>115944238</v>
       </c>
       <c r="B4" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -937,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530487</v>
+        <v>530395</v>
       </c>
       <c r="R4" t="n">
-        <v>7237338</v>
+        <v>7237307</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +971,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -997,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1011,12 +996,7 @@
         <v>115944252</v>
       </c>
       <c r="B5" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,37 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115944242</v>
+        <v>115944206</v>
       </c>
       <c r="B6" t="n">
-        <v>97680</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530308</v>
+        <v>530510</v>
       </c>
       <c r="R6" t="n">
-        <v>7237304</v>
+        <v>7237349</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,7 +1187,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>5722</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1223,7 +1198,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Julia Svensson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1234,55 +1209,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115944254</v>
+        <v>115944246</v>
       </c>
       <c r="B7" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530327</v>
+        <v>530410</v>
       </c>
       <c r="R7" t="n">
-        <v>7237295</v>
+        <v>7237302</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1317,11 +1282,6 @@
           <t>2023-06-16</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hackade i gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1333,7 +1293,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>5713</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1355,37 +1315,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115944246</v>
+        <v>115944241</v>
       </c>
       <c r="B8" t="n">
-        <v>94068</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1395,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530410</v>
+        <v>530393</v>
       </c>
       <c r="R8" t="n">
-        <v>7237302</v>
+        <v>7237304</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1444,7 +1399,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5729</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1466,37 +1421,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115944264</v>
+        <v>115944267</v>
       </c>
       <c r="B9" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1506,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530384</v>
+        <v>530334</v>
       </c>
       <c r="R9" t="n">
-        <v>7237281</v>
+        <v>7237280</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1555,7 +1505,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1566,7 +1516,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Julia Svensson</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1577,15 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115944241</v>
+        <v>115944264</v>
       </c>
       <c r="B10" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,21 +1538,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1617,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530393</v>
+        <v>530384</v>
       </c>
       <c r="R10" t="n">
-        <v>7237304</v>
+        <v>7237281</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1666,7 +1611,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>5729</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1677,7 +1622,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Julia Svensson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1688,15 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115944239</v>
+        <v>115944254</v>
       </c>
       <c r="B11" t="n">
-        <v>77463</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,34 +1644,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530379</v>
+        <v>530327</v>
       </c>
       <c r="R11" t="n">
-        <v>7237307</v>
+        <v>7237295</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1766,6 +1711,11 @@
           <t>2023-06-16</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hackade i gran</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1777,7 +1727,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>5728</t>
+          <t>5713</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1799,15 +1749,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115944245</v>
+        <v>115944263</v>
       </c>
       <c r="B12" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,34 +1760,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530431</v>
+        <v>530419</v>
       </c>
       <c r="R12" t="n">
-        <v>7237302</v>
+        <v>7237285</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1888,7 +1838,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>5743</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1899,7 +1849,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Julia Svensson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1910,37 +1860,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115944269</v>
+        <v>115944242</v>
       </c>
       <c r="B13" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1950,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530386</v>
+        <v>530308</v>
       </c>
       <c r="R13" t="n">
-        <v>7237276</v>
+        <v>7237304</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1999,7 +1944,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2014,117 +1959,6 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>115944238</v>
-      </c>
-      <c r="B14" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>864</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Knottrig blåslav</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Hypogymnia bitteri</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>530395</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7237307</v>
-      </c>
-      <c r="S14" t="n">
-        <v>5</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2023-06-16</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2023-06-16</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>5733</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
         <is>
           <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
         </is>
